--- a/docs/Topic5.1_SharpeRatioExamples_Revised.xlsx
+++ b/docs/Topic5.1_SharpeRatioExamples_Revised.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerry\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerry\repos\mgmt675-2025\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5E0D26-63F8-4DC6-8502-DAA3BF1EA268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022EF21D-64F4-47C4-96DE-450EA1A8D953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3218" yWindow="3218" windowWidth="16200" windowHeight="9982" tabRatio="787" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="787" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Applied" sheetId="25" r:id="rId1"/>
-    <sheet name="Equations" sheetId="43" r:id="rId2"/>
+    <sheet name="Equation Method" sheetId="43" r:id="rId2"/>
     <sheet name="5.5.2 MCSI MktCaps" sheetId="32" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -143,7 +143,7 @@
     <definedName name="RiskUseFixedSeed" hidden="1">FALSE</definedName>
     <definedName name="RiskUseMultipleCPUs" hidden="1">FALSE</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Applied!$C$17:$E$17</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">Equations!$C$17:$E$17</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'Equation Method'!$C$17:$E$17</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
@@ -155,9 +155,9 @@
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">Applied!$F$17</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Equations!$F$17</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Equation Method'!$F$17</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">Applied!$G$17</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">Equations!$G$17</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'Equation Method'!$G$17</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
@@ -175,7 +175,7 @@
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">Applied!$J$17</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">Equations!$J$17</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'Equation Method'!$J$17</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
@@ -187,7 +187,7 @@
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">Applied!$B$17</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">Equations!$B$17</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'Equation Method'!$B$17</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
@@ -252,7 +252,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
   <si>
     <t>Domestic Equity</t>
   </si>
@@ -331,19 +331,20 @@
   <si>
     <t>Risk premia</t>
   </si>
+  <si>
+    <t>Risk Limit (std dev)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000%"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00000000"/>
-    <numFmt numFmtId="175" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -560,10 +561,10 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -571,8 +572,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -585,14 +586,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -608,21 +609,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -631,17 +632,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -924,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1070,11 +1066,11 @@
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
@@ -1101,7 +1097,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B17" s="42"/>
       <c r="C17" s="11">
         <v>0.42029973062798409</v>
@@ -1116,192 +1112,96 @@
         <f>SUM(C17:E17)</f>
         <v>0.99999993860448222</v>
       </c>
-      <c r="G17" s="50" cm="1">
+      <c r="G17" s="9" cm="1">
         <f t="array" ref="G17">MMULT(C17:E17,TRANSPOSE($C$4:$E$4))</f>
         <v>6.6306257423518894E-2</v>
       </c>
-      <c r="H17" s="50" cm="1">
+      <c r="H17" s="9" cm="1">
         <f t="array" ref="H17">SQRT(MMULT(C17:E17,MMULT($C$8:$E$10,TRANSPOSE(C17:E17))))</f>
         <v>0.15430053913614955</v>
       </c>
-      <c r="I17" s="52">
+      <c r="I17" s="49">
         <f>(G17-C12)/H17</f>
         <v>0.39861336692574911</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C18" s="8"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C19" s="8"/>
-      <c r="J19" s="51"/>
-    </row>
-    <row r="20" spans="2:11" ht="29" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C20" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="2:11" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B22" s="43">
-        <v>0.04</v>
-      </c>
-      <c r="C22" s="16">
-        <v>1.6002637950748135</v>
-      </c>
-      <c r="D22" s="16">
-        <v>0.53298160655047899</v>
-      </c>
-      <c r="E22" s="16">
-        <v>-1.1332454016252924</v>
-      </c>
-      <c r="F22" s="16">
-        <f>SUM(C22:E22)</f>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="G22" s="9" cm="1">
-        <f t="array" ref="G22">MMULT(C22:E22,TRANSPOSE($C$4:$E$4))</f>
-        <v>4.0000000000246533E-2</v>
-      </c>
-      <c r="H22" s="9" cm="1">
-        <f t="array" ref="H22">SQRT(MMULT(C22:E22,MMULT($C$8:$E$10,TRANSPOSE(C22:E22))))</f>
-        <v>0.1912380680730402</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B23" s="44">
-        <v>0.05</v>
-      </c>
-      <c r="C23" s="9">
-        <v>1.1517150260908089</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0.46437998353034776</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.61609500962115649</v>
-      </c>
-      <c r="F23" s="9">
-        <f t="shared" ref="F23:F26" si="0">SUM(C23:E23)</f>
-        <v>1</v>
-      </c>
-      <c r="G23" s="9" cm="1">
-        <f t="array" ref="G23">MMULT(C23:E23,TRANSPOSE($C$4:$E$4))</f>
-        <v>4.9999999725228617E-2</v>
-      </c>
-      <c r="H23" s="9" cm="1">
-        <f t="array" ref="H23">SQRT(MMULT(C23:E23,MMULT($C$8:$E$10,TRANSPOSE(C23:E23))))</f>
-        <v>0.1546409372626861</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B24" s="44">
-        <v>0.06</v>
-      </c>
-      <c r="C24" s="11">
-        <v>0.70316619583171769</v>
-      </c>
-      <c r="D24" s="11">
-        <v>0.39577833383406508</v>
-      </c>
-      <c r="E24" s="11">
-        <v>-9.8944538869047222E-2</v>
-      </c>
-      <c r="F24" s="9">
-        <f t="shared" si="0"/>
-        <v>0.99999999079673552</v>
-      </c>
-      <c r="G24" s="9" cm="1">
-        <f t="array" ref="G24">MMULT(C24:E24,TRANSPOSE($C$4:$E$4))</f>
-        <v>6.0000000339593518E-2</v>
-      </c>
-      <c r="H24" s="9" cm="1">
-        <f t="array" ref="H24">SQRT(MMULT(C24:E24,MMULT($C$8:$E$10,TRANSPOSE(C24:E24))))</f>
-        <v>0.14432709307305036</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B25" s="44">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C25" s="11">
-        <v>0.25461712220640237</v>
-      </c>
-      <c r="D25" s="11">
-        <v>0.32717693430631439</v>
-      </c>
-      <c r="E25" s="11">
-        <v>0.41820594265376526</v>
-      </c>
-      <c r="F25" s="9">
-        <f t="shared" si="0"/>
-        <v>0.99999999916648208</v>
-      </c>
-      <c r="G25" s="9" cm="1">
-        <f t="array" ref="G25">MMULT(C25:E25,TRANSPOSE($C$4:$E$4))</f>
-        <v>7.0000003474595798E-2</v>
-      </c>
-      <c r="H25" s="9" cm="1">
-        <f t="array" ref="H25">SQRT(MMULT(C25:E25,MMULT($C$8:$E$10,TRANSPOSE(C25:E25))))</f>
-        <v>0.16529208969377709</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="45">
-        <v>0.08</v>
-      </c>
-      <c r="C26" s="47">
-        <v>-0.19393142539494257</v>
-      </c>
-      <c r="D26" s="47">
-        <v>0.25857526376446238</v>
-      </c>
-      <c r="E26" s="47">
-        <v>0.93535616862816451</v>
-      </c>
-      <c r="F26" s="17">
-        <f t="shared" si="0"/>
-        <v>1.0000000069976842</v>
-      </c>
-      <c r="G26" s="17" cm="1">
-        <f t="array" ref="G26">MMULT(C26:E26,TRANSPOSE($C$4:$E$4))</f>
-        <v>8.0000000111246666E-2</v>
-      </c>
-      <c r="H26" s="17" cm="1">
-        <f t="array" ref="H26">SQRT(MMULT(C26:E26,MMULT($C$8:$E$10,TRANSPOSE(C26:E26))))</f>
-        <v>0.20829618763345809</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
@@ -1310,7 +1210,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -1319,7 +1219,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
@@ -1328,7 +1228,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -1337,7 +1237,7 @@
       <c r="I30" s="9"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
@@ -1346,7 +1246,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -2156,100 +2056,9 @@
       <c r="I121" s="9"/>
       <c r="J121" s="2"/>
     </row>
-    <row r="122" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="2"/>
-      <c r="I122" s="9"/>
-      <c r="J122" s="2"/>
-    </row>
-    <row r="123" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="9"/>
-      <c r="J123" s="2"/>
-    </row>
-    <row r="124" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="2"/>
-      <c r="I124" s="9"/>
-      <c r="J124" s="2"/>
-    </row>
-    <row r="125" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="9"/>
-      <c r="J125" s="2"/>
-    </row>
-    <row r="126" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="9"/>
-      <c r="J126" s="2"/>
-    </row>
-    <row r="127" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="9"/>
-      <c r="J127" s="2"/>
-    </row>
-    <row r="128" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="2"/>
-      <c r="I128" s="9"/>
-      <c r="J128" s="2"/>
-    </row>
-    <row r="129" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="9"/>
-      <c r="J129" s="2"/>
-    </row>
-    <row r="130" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="2"/>
-      <c r="I130" s="9"/>
-      <c r="J130" s="2"/>
-    </row>
-    <row r="131" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="9"/>
-      <c r="J131" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C20:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2257,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D78357-FEB1-4B6E-8930-AD854AA2B414}">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2388,25 +2197,25 @@
       <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="50">
         <f>0.0012*4</f>
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="50">
         <f>C4-$C$12</f>
         <v>5.5199999999999999E-2</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="50">
         <f t="shared" ref="D13:E13" si="0">D4-$C$12</f>
         <v>6.0200000000000004E-2</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="50">
         <f t="shared" si="0"/>
         <v>7.5200000000000003E-2</v>
       </c>
@@ -2417,11 +2226,11 @@
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
@@ -2471,218 +2280,242 @@
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
+      <c r="C18" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C17)</f>
+        <v>{=TRANSPOSE(MMULT(MINVERSE(C8:E10), TRANSPOSE(C13:E13)))}</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C19" s="11">
         <f>C17/$F$17</f>
         <v>0.42029951056541748</v>
       </c>
-      <c r="D18" s="11">
-        <f t="shared" ref="D18:E18" si="1">D17/$F$17</f>
+      <c r="D19" s="11">
+        <f t="shared" ref="D19:E19" si="1">D17/$F$17</f>
         <v>0.35251639573353422</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E19" s="11">
         <f t="shared" si="1"/>
         <v>0.22718409370104833</v>
       </c>
-      <c r="F18" s="9">
-        <f>SUM(C18:E18)</f>
+      <c r="F19" s="9">
+        <f>SUM(C19:E19)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="9" cm="1">
-        <f t="array" ref="G18">MMULT(C18:E18,TRANSPOSE($C$4:$E$4))</f>
+      <c r="G19" s="9" cm="1">
+        <f t="array" ref="G19">MMULT(C19:E19,TRANSPOSE($C$4:$E$4))</f>
         <v>6.6306263852688646E-2</v>
       </c>
-      <c r="H18" s="9" cm="1">
-        <f t="array" ref="H18">SQRT(MMULT(C18:E18,MMULT($C$8:$E$10,TRANSPOSE(C18:E18))))</f>
+      <c r="H19" s="9" cm="1">
+        <f t="array" ref="H19">SQRT(MMULT(C19:E19,MMULT($C$8:$E$10,TRANSPOSE(C19:E19))))</f>
         <v>0.1543005545256747</v>
       </c>
-      <c r="I18" s="2">
-        <f>(G18-C12)/H18</f>
+      <c r="I19" s="2">
+        <f>(G19-C12)/H19</f>
         <v>0.39861336883565357</v>
       </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C19" s="8"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="2:11" ht="29" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C20" s="49" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C20" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C19)</f>
+        <v>=C17/$F$17</v>
+      </c>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="2:11" ht="29" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="2:11" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="4" t="s">
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="2:11" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C22" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D22" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E22" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F22" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G22" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H22" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B22" s="43">
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B23" s="43">
         <v>0.04</v>
       </c>
-      <c r="C22" s="16">
-        <v>1.6002637950748135</v>
-      </c>
-      <c r="D22" s="16">
-        <v>0.53298160655047899</v>
-      </c>
-      <c r="E22" s="16">
-        <v>-1.1332454016252924</v>
-      </c>
-      <c r="F22" s="16">
-        <f>SUM(C22:E22)</f>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="G22" s="9" cm="1">
-        <f t="array" ref="G22">MMULT(C22:E22,TRANSPOSE($C$4:$E$4))</f>
-        <v>4.0000000000246533E-2</v>
-      </c>
-      <c r="H22" s="9" cm="1">
-        <f t="array" ref="H22">SQRT(MMULT(C22:E22,MMULT($C$8:$E$10,TRANSPOSE(C22:E22))))</f>
-        <v>0.1912380680730402</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B23" s="44">
-        <v>0.05</v>
-      </c>
-      <c r="C23" s="9">
-        <v>1.1517150260908089</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0.46437998353034776</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.61609500962115649</v>
-      </c>
-      <c r="F23" s="9">
-        <f t="shared" ref="F23:F26" si="2">SUM(C23:E23)</f>
-        <v>1</v>
+      <c r="C23" s="16">
+        <f>C$19 * ($B23 -$C$12) / ($G$19-$C$12)</f>
+        <v>0.24053717207301928</v>
+      </c>
+      <c r="D23" s="16">
+        <f t="shared" ref="D23:E27" si="2">D$19 * ($B23 -$C$12) / ($G$19-$C$12)</f>
+        <v>0.20174493380933889</v>
+      </c>
+      <c r="E23" s="16">
+        <f t="shared" si="2"/>
+        <v>0.13001732827456292</v>
+      </c>
+      <c r="F23" s="16">
+        <f>SUM(C23:E23)</f>
+        <v>0.57229943415692108</v>
       </c>
       <c r="G23" s="9" cm="1">
-        <f t="array" ref="G23">MMULT(C23:E23,TRANSPOSE($C$4:$E$4))</f>
-        <v>4.9999999725228617E-2</v>
+        <f t="array" ref="G23">MMULT(C23:E23,TRANSPOSE($C$4:$E$4))+(1-F23)*$C$12</f>
+        <v>3.9999999999999994E-2</v>
       </c>
       <c r="H23" s="9" cm="1">
         <f t="array" ref="H23">SQRT(MMULT(C23:E23,MMULT($C$8:$E$10,TRANSPOSE(C23:E23))))</f>
-        <v>0.1546409372626861</v>
+        <v>8.8306120045142794E-2</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B24" s="44">
-        <v>0.06</v>
-      </c>
-      <c r="C24" s="11">
-        <v>0.70316619583171769</v>
-      </c>
-      <c r="D24" s="11">
-        <v>0.39577833383406508</v>
-      </c>
-      <c r="E24" s="11">
-        <v>-9.8944538869047222E-2</v>
+        <v>0.05</v>
+      </c>
+      <c r="C24" s="9">
+        <f t="shared" ref="C24:C27" si="3">C$19 * ($B24 -$C$12) / ($G$19-$C$12)</f>
+        <v>0.30887159595739982</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" si="2"/>
+        <v>0.25905883545971931</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="2"/>
+        <v>0.16695406926165465</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="2"/>
-        <v>0.99999999079673552</v>
+        <f t="shared" ref="F24:F27" si="4">SUM(C24:E24)</f>
+        <v>0.73488450067877387</v>
       </c>
       <c r="G24" s="9" cm="1">
-        <f t="array" ref="G24">MMULT(C24:E24,TRANSPOSE($C$4:$E$4))</f>
-        <v>6.0000000339593518E-2</v>
+        <f t="array" ref="G24">MMULT(C24:E24,TRANSPOSE($C$4:$E$4))+(1-F24)*$C$12</f>
+        <v>0.05</v>
       </c>
       <c r="H24" s="9" cm="1">
         <f t="array" ref="H24">SQRT(MMULT(C24:E24,MMULT($C$8:$E$10,TRANSPOSE(C24:E24))))</f>
-        <v>0.14432709307305036</v>
+        <v>0.11339308596705837</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B25" s="44">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="C25" s="11">
-        <v>0.25461712220640237</v>
+        <f t="shared" si="3"/>
+        <v>0.3772060198417802</v>
       </c>
       <c r="D25" s="11">
-        <v>0.32717693430631439</v>
+        <f t="shared" si="2"/>
+        <v>0.31637273711009967</v>
       </c>
       <c r="E25" s="11">
-        <v>0.41820594265376526</v>
+        <f t="shared" si="2"/>
+        <v>0.20389081024874636</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="2"/>
-        <v>0.99999999916648208</v>
+        <f t="shared" si="4"/>
+        <v>0.89746956720062621</v>
       </c>
       <c r="G25" s="9" cm="1">
-        <f t="array" ref="G25">MMULT(C25:E25,TRANSPOSE($C$4:$E$4))</f>
-        <v>7.0000003474595798E-2</v>
+        <f t="array" ref="G25">MMULT(C25:E25,TRANSPOSE($C$4:$E$4))+(1-F25)*$C$12</f>
+        <v>5.9999999999999991E-2</v>
       </c>
       <c r="H25" s="9" cm="1">
         <f t="array" ref="H25">SQRT(MMULT(C25:E25,MMULT($C$8:$E$10,TRANSPOSE(C25:E25))))</f>
-        <v>0.16529208969377709</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="45">
+        <v>0.13848005188897392</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B26" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C26" s="11">
+        <f t="shared" si="3"/>
+        <v>0.44554044372616081</v>
+      </c>
+      <c r="D26" s="11">
+        <f t="shared" si="2"/>
+        <v>0.37368663876048003</v>
+      </c>
+      <c r="E26" s="11">
+        <f t="shared" si="2"/>
+        <v>0.24082755123583813</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="4"/>
+        <v>1.060054633722479</v>
+      </c>
+      <c r="G26" s="9" cm="1">
+        <f t="array" ref="G26">MMULT(C26:E26,TRANSPOSE($C$4:$E$4))+(1-F26)*$C$12</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H26" s="9" cm="1">
+        <f t="array" ref="H26">SQRT(MMULT(C26:E26,MMULT($C$8:$E$10,TRANSPOSE(C26:E26))))</f>
+        <v>0.1635670178108895</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="45">
         <v>0.08</v>
       </c>
-      <c r="C26" s="47">
-        <v>-0.19393142539494257</v>
-      </c>
-      <c r="D26" s="47">
-        <v>0.25857526376446238</v>
-      </c>
-      <c r="E26" s="47">
-        <v>0.93535616862816451</v>
-      </c>
-      <c r="F26" s="17">
+      <c r="C27" s="47">
+        <f t="shared" si="3"/>
+        <v>0.51387486761054124</v>
+      </c>
+      <c r="D27" s="47">
         <f t="shared" si="2"/>
-        <v>1.0000000069976842</v>
-      </c>
-      <c r="G26" s="17" cm="1">
-        <f t="array" ref="G26">MMULT(C26:E26,TRANSPOSE($C$4:$E$4))</f>
-        <v>8.0000000111246666E-2</v>
-      </c>
-      <c r="H26" s="17" cm="1">
-        <f t="array" ref="H26">SQRT(MMULT(C26:E26,MMULT($C$8:$E$10,TRANSPOSE(C26:E26))))</f>
-        <v>0.20829618763345809</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="2"/>
+        <v>0.43100054041086039</v>
+      </c>
+      <c r="E27" s="47">
+        <f t="shared" si="2"/>
+        <v>0.27776429222292986</v>
+      </c>
+      <c r="F27" s="17">
+        <f t="shared" si="4"/>
+        <v>1.2226397002443314</v>
+      </c>
+      <c r="G27" s="17" cm="1">
+        <f t="array" ref="G27">MMULT(C27:E27,TRANSPOSE($C$4:$E$4))+(1-F27)*$C$12</f>
+        <v>7.9999999999999988E-2</v>
+      </c>
+      <c r="H27" s="17" cm="1">
+        <f t="array" ref="H27">SQRT(MMULT(C27:E27,MMULT($C$8:$E$10,TRANSPOSE(C27:E27))))</f>
+        <v>0.18865398373280506</v>
+      </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C28" s="9"/>
+      <c r="C28" s="9" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C27)</f>
+        <v>=C$19 * ($B27 -$C$12) / ($G$19-$C$12)</v>
+      </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="G28" s="9"/>
@@ -2700,69 +2533,195 @@
       <c r="J29" s="2"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="2"/>
+      <c r="C30" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
       <c r="I30" s="9"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="2"/>
+    <row r="31" spans="2:11" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="46" t="s">
+        <v>6</v>
+      </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="2"/>
+      <c r="B32" s="43">
+        <v>0.08</v>
+      </c>
+      <c r="C32" s="16">
+        <f>C$19 * $B32 / $H$19</f>
+        <v>0.21791211929597162</v>
+      </c>
+      <c r="D32" s="16">
+        <f t="shared" ref="D32:E36" si="5">D$19 * $B32 / $H$19</f>
+        <v>0.18276869934378753</v>
+      </c>
+      <c r="E32" s="16">
+        <f t="shared" si="5"/>
+        <v>0.11778783006939679</v>
+      </c>
+      <c r="F32" s="16">
+        <f>SUM(C32:E32)</f>
+        <v>0.51846864870915588</v>
+      </c>
+      <c r="G32" s="9" cm="1">
+        <f t="array" ref="G32">MMULT(C32:E32,TRANSPOSE($C$4:$E$4))</f>
+        <v>3.4377719020656235E-2</v>
+      </c>
+      <c r="H32" s="9" cm="1">
+        <f t="array" ref="H32">SQRT(MMULT(C32:E32,MMULT($C$8:$E$10,TRANSPOSE(C32:E32))))</f>
+        <v>0.08</v>
+      </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="2"/>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B33" s="44">
+        <v>0.11</v>
+      </c>
+      <c r="C33" s="9">
+        <f t="shared" ref="C33:C36" si="6">C$19 * $B33 / $H$19</f>
+        <v>0.29962916403196094</v>
+      </c>
+      <c r="D33" s="9">
+        <f t="shared" si="5"/>
+        <v>0.25130696159770788</v>
+      </c>
+      <c r="E33" s="9">
+        <f t="shared" si="5"/>
+        <v>0.1619582663454206</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" ref="F33:F36" si="7">SUM(C33:E33)</f>
+        <v>0.71289439197508941</v>
+      </c>
+      <c r="G33" s="9" cm="1">
+        <f t="array" ref="G33">MMULT(C33:E33,TRANSPOSE($C$4:$E$4))</f>
+        <v>4.7269363653402313E-2</v>
+      </c>
+      <c r="H33" s="9" cm="1">
+        <f t="array" ref="H33">SQRT(MMULT(C33:E33,MMULT($C$8:$E$10,TRANSPOSE(C33:E33))))</f>
+        <v>0.11</v>
+      </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="2"/>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B34" s="44">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C34" s="11">
+        <f t="shared" si="6"/>
+        <v>0.38134620876795033</v>
+      </c>
+      <c r="D34" s="11">
+        <f t="shared" si="5"/>
+        <v>0.31984522385162822</v>
+      </c>
+      <c r="E34" s="11">
+        <f t="shared" si="5"/>
+        <v>0.20612870262144442</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" si="7"/>
+        <v>0.90732013524102295</v>
+      </c>
+      <c r="G34" s="9" cm="1">
+        <f t="array" ref="G34">MMULT(C34:E34,TRANSPOSE($C$4:$E$4))</f>
+        <v>6.0161008286148412E-2</v>
+      </c>
+      <c r="H34" s="9" cm="1">
+        <f t="array" ref="H34">SQRT(MMULT(C34:E34,MMULT($C$8:$E$10,TRANSPOSE(C34:E34))))</f>
+        <v>0.14000000000000001</v>
+      </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2"/>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="2"/>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B35" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="C35" s="11">
+        <f t="shared" si="6"/>
+        <v>0.46306325350393973</v>
+      </c>
+      <c r="D35" s="11">
+        <f t="shared" si="5"/>
+        <v>0.38838348610554857</v>
+      </c>
+      <c r="E35" s="11">
+        <f t="shared" si="5"/>
+        <v>0.25029913889746819</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="7"/>
+        <v>1.1017458785069565</v>
+      </c>
+      <c r="G35" s="9" cm="1">
+        <f t="array" ref="G35">MMULT(C35:E35,TRANSPOSE($C$4:$E$4))</f>
+        <v>7.3052652918894498E-2</v>
+      </c>
+      <c r="H35" s="9" cm="1">
+        <f t="array" ref="H35">SQRT(MMULT(C35:E35,MMULT($C$8:$E$10,TRANSPOSE(C35:E35))))</f>
+        <v>0.17000000000000004</v>
+      </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2"/>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="2"/>
+    <row r="36" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B36" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="C36" s="47">
+        <f t="shared" si="6"/>
+        <v>0.54478029823992913</v>
+      </c>
+      <c r="D36" s="47">
+        <f t="shared" si="5"/>
+        <v>0.45692174835946886</v>
+      </c>
+      <c r="E36" s="47">
+        <f t="shared" si="5"/>
+        <v>0.29446957517349198</v>
+      </c>
+      <c r="F36" s="17">
+        <f t="shared" si="7"/>
+        <v>1.29617162177289</v>
+      </c>
+      <c r="G36" s="17" cm="1">
+        <f t="array" ref="G36">MMULT(C36:E36,TRANSPOSE($C$4:$E$4))</f>
+        <v>8.5944297551640583E-2</v>
+      </c>
+      <c r="H36" s="17" cm="1">
+        <f t="array" ref="H36">SQRT(MMULT(C36:E36,MMULT($C$8:$E$10,TRANSPOSE(C36:E36))))</f>
+        <v>0.2</v>
+      </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2"/>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -2771,7 +2730,7 @@
       <c r="I37" s="9"/>
       <c r="J37" s="2"/>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -2780,7 +2739,7 @@
       <c r="I38" s="9"/>
       <c r="J38" s="2"/>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -2789,7 +2748,7 @@
       <c r="I39" s="9"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -2798,7 +2757,7 @@
       <c r="I40" s="9"/>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -2807,7 +2766,7 @@
       <c r="I41" s="9"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -2816,7 +2775,7 @@
       <c r="I42" s="9"/>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -2825,7 +2784,7 @@
       <c r="I43" s="9"/>
       <c r="J43" s="2"/>
     </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -2834,7 +2793,7 @@
       <c r="I44" s="9"/>
       <c r="J44" s="2"/>
     </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -2843,7 +2802,7 @@
       <c r="I45" s="9"/>
       <c r="J45" s="2"/>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -2852,7 +2811,7 @@
       <c r="I46" s="9"/>
       <c r="J46" s="2"/>
     </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -2861,7 +2820,7 @@
       <c r="I47" s="9"/>
       <c r="J47" s="2"/>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -3617,10 +3576,20 @@
       <c r="I131" s="9"/>
       <c r="J131" s="2"/>
     </row>
+    <row r="132" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C30:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
